--- a/output/pdf_financials_xlsx/HELI.xlsx
+++ b/output/pdf_financials_xlsx/HELI.xlsx
@@ -634,7 +634,7 @@
         <v>0.008891</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.060835</v>
+        <v>0.224863</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.026905</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.106948</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>1.457981</v>
@@ -4312,7 +4312,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -5602,7 +5606,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.026905</v>
       </c>
@@ -14302,7 +14310,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HELI.xlsx
+++ b/output/pdf_financials_xlsx/HELI.xlsx
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00053</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004067</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.041004</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.080091</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000294</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016519</v>
       </c>
     </row>
     <row r="13">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.560296</v>
+        <v>-0.560826</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.523676</v>
+        <v>-0.527743</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.465838</v>
+        <v>-0.506842</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.932908</v>
+        <v>-6.852817</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.195555</v>
+        <v>-3.195261</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.195555</v>
+        <v>-3.179036</v>
       </c>
     </row>
     <row r="28">
@@ -1156,22 +1156,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.559537</v>
+        <v>-0.560067</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.523676</v>
+        <v>-0.527743</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.465838</v>
+        <v>-0.506842</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.932908</v>
+        <v>-6.852817</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.195555</v>
+        <v>-3.195261</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.195555</v>
+        <v>-3.179036</v>
       </c>
     </row>
     <row r="30">
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-13.68188252985509</v>
+        <v>-14.88618941605625</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-120.5749971477626</v>
+        <v>-119.1820791836757</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-338.5666971800544</v>
+        <v>-338.5355480967274</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-1208.857742722578</v>
+        <v>-1202.608712099718</v>
       </c>
     </row>
     <row r="31">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001917</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.469367</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>5.530473</v>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001917</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.469367</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>5.530473</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.02174</v>
+        <v>0.019823</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.682768</v>
+        <v>8.213400999999999</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.06904100000000001</v>
@@ -3824,13 +3824,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.034923</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.094944</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06329600000000001</v>
       </c>
     </row>
     <row r="125">
@@ -3849,13 +3849,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.034923</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.094944</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06329600000000001</v>
       </c>
     </row>
     <row r="126">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -6372,7 +6372,11 @@
           <t>Lease payment (Note 13)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -7024,7 +7028,11 @@
           <t>Lease payment (Note 12)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7434,7 +7442,11 @@
           <t>Lease payment (Note 15)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -11644,7 +11656,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14682,7 +14694,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">
@@ -15096,7 +15108,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">
